--- a/data/query.xlsx
+++ b/data/query.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>当月</t>
+          <t>当日(发送当天)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>__TODAY__</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>__TODAY__</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>期望 Err&gt;=0 返回条件单列表</t>
+          <t>当日窗口：命中当天 create 造的单（Begin=End=__TODAY__，发送时展开当天）</t>
         </is>
       </c>
     </row>
